--- a/medical_surveys_questionnaires/044_respirator_medical_evaluation_questionnaire--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/044_respirator_medical_evaluation_questionnaire--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'penicillin'}</t>
+          <t>penicillin</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Penicillin'}</t>
+          <t>Penicillin</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'aspirin'}</t>
+          <t>aspirin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Aspirin'}</t>
+          <t>Aspirin</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'using_a_respirator'}</t>
+          <t>using_a_respirator</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Using a respirator'}</t>
+          <t>Using a respirator</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'left_leg'}</t>
+          <t>left_leg</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Left Leg'}</t>
+          <t>Left Leg</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'right_leg'}</t>
+          <t>right_leg</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Right Leg'}</t>
+          <t>Right Leg</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'ventilator'}</t>
+          <t>ventilator</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Ventilator'}</t>
+          <t>Ventilator</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'non-invasive_positive_pressure_ventilation'}</t>
+          <t>non-invasive_positive_pressure_ventilation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Non-invasive positive pressure ventilation'}</t>
+          <t>Non-invasive positive pressure ventilation</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
